--- a/144/DQ Templates and Instructions/Topic 2 DQ 1/Topic 2 DQ 1.xlsx
+++ b/144/DQ Templates and Instructions/Topic 2 DQ 1/Topic 2 DQ 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 2 DQ 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="8_{EC0CA368-B35E-4E61-BE63-B68E8477FF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C35975E-E1B7-48B2-A382-C8B3F7ADDE00}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="8_{EC0CA368-B35E-4E61-BE63-B68E8477FF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5232D9C-7D1B-464C-9057-BBC2BB43756E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30DCFED0-AF9F-4763-8D9E-1F0E9BEB0013}"/>
   </bookViews>
@@ -39,8 +39,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={17256E4C-17C3-4B8E-B4B3-9DBC2479A261}</author>
+  </authors>
+  <commentList>
+    <comment ref="F33" authorId="0" shapeId="0" xr:uid="{17256E4C-17C3-4B8E-B4B3-9DBC2479A261}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    https://youtu.be/0kVtUP0Dwb8</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="135">
   <si>
     <t>Excel Skills Learned</t>
   </si>
@@ -554,6 +572,9 @@
       <t>Note: Only the "Final quantity" and "Final units" can be auto-graded, as there are many ways that you might enter your conversion ratios. All formula cells are checked for formulas. As always, your formulas should use cell references, but the autograder can't check for that.</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">Video explanations to follow along with A and B. </t>
+  </si>
 </sst>
 </file>
 
@@ -563,7 +584,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -658,6 +679,20 @@
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1747,6 +1782,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1774,72 +1827,227 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1849,156 +2057,83 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2039,9 +2174,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
@@ -2050,30 +2182,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2101,90 +2209,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2353,6 +2388,12 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Richard Ketchersid" id="{97F34F03-09C1-44D2-ADC1-769671B2CFF1}" userId="S::richard.ketchersid@gcu.edu::a14ec2f7-27bd-40c3-90d9-209834cdef57" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2650,6 +2691,20 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="F33" dT="2026-07-16T19:34:26.77" personId="{97F34F03-09C1-44D2-ADC1-769671B2CFF1}" id="{17256E4C-17C3-4B8E-B4B3-9DBC2479A261}">
+    <text>https://youtu.be/0kVtUP0Dwb8</text>
+    <extLst>
+      <x:ext xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" uri="{F7C98A9C-CBB3-438F-8F68-D28B6AF4A901}">
+        <xltc2:checksum>2599167450</xltc2:checksum>
+        <xltc2:hyperlink startIndex="0" length="28" url="https://youtu.be/0kVtUP0Dwb8"/>
+      </x:ext>
+    </extLst>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D612F618-95E1-43F2-9FA9-C26EFDC8D807}">
   <dimension ref="B1:I10"/>
@@ -2663,63 +2718,63 @@
       <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="89" t="s">
+      <c r="D2" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="91"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="99"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="92"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="94"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="102"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="92"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="94"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="102"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="92"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="94"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="102"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="D6" s="92"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="94"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="101"/>
+      <c r="F6" s="101"/>
+      <c r="G6" s="101"/>
+      <c r="H6" s="101"/>
+      <c r="I6" s="102"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1">
-      <c r="D7" s="95"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
-      <c r="H7" s="96"/>
-      <c r="I7" s="97"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="104"/>
+      <c r="I7" s="105"/>
     </row>
     <row r="8" spans="2:9" ht="19.5" thickBot="1">
       <c r="B8" s="52" t="s">
@@ -2747,7 +2802,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C781E8-8BCA-4604-9AA0-98AEDF949CBB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C781E8-8BCA-4604-9AA0-98AEDF949CBB}">
   <dimension ref="A1:T41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2759,659 +2814,659 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="128"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="108"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="129"/>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="131"/>
+      <c r="A2" s="109"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="111"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="129"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="131"/>
+      <c r="A3" s="109"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="110"/>
+      <c r="M3" s="110"/>
+      <c r="N3" s="110"/>
+      <c r="O3" s="110"/>
+      <c r="P3" s="111"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="129"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="130"/>
-      <c r="P4" s="131"/>
+      <c r="A4" s="109"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110"/>
+      <c r="P4" s="111"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="129"/>
-      <c r="B5" s="130"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="130"/>
-      <c r="N5" s="130"/>
-      <c r="O5" s="130"/>
-      <c r="P5" s="131"/>
+      <c r="A5" s="109"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="110"/>
+      <c r="L5" s="110"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="110"/>
+      <c r="P5" s="111"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="129"/>
-      <c r="B6" s="130"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="130"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="131"/>
+      <c r="A6" s="109"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="110"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="110"/>
+      <c r="O6" s="110"/>
+      <c r="P6" s="111"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="129"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="131"/>
+      <c r="A7" s="109"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="111"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="129"/>
-      <c r="B8" s="130"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="130"/>
-      <c r="I8" s="130"/>
-      <c r="J8" s="130"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="130"/>
-      <c r="N8" s="130"/>
-      <c r="O8" s="130"/>
-      <c r="P8" s="131"/>
+      <c r="A8" s="109"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="110"/>
+      <c r="L8" s="110"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="110"/>
+      <c r="P8" s="111"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="129"/>
-      <c r="B9" s="130"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="130"/>
-      <c r="I9" s="130"/>
-      <c r="J9" s="130"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="130"/>
-      <c r="N9" s="130"/>
-      <c r="O9" s="130"/>
-      <c r="P9" s="131"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="110"/>
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="110"/>
+      <c r="K9" s="110"/>
+      <c r="L9" s="110"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="110"/>
+      <c r="P9" s="111"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="129"/>
-      <c r="B10" s="130"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="130"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="130"/>
-      <c r="K10" s="130"/>
-      <c r="L10" s="130"/>
-      <c r="M10" s="130"/>
-      <c r="N10" s="130"/>
-      <c r="O10" s="130"/>
-      <c r="P10" s="131"/>
+      <c r="A10" s="109"/>
+      <c r="B10" s="110"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="110"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="111"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A11" s="132"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="133"/>
-      <c r="K11" s="133"/>
-      <c r="L11" s="133"/>
-      <c r="M11" s="133"/>
-      <c r="N11" s="133"/>
-      <c r="O11" s="133"/>
-      <c r="P11" s="134"/>
+      <c r="A11" s="112"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="113"/>
+      <c r="F11" s="113"/>
+      <c r="G11" s="113"/>
+      <c r="H11" s="113"/>
+      <c r="I11" s="113"/>
+      <c r="J11" s="113"/>
+      <c r="K11" s="113"/>
+      <c r="L11" s="113"/>
+      <c r="M11" s="113"/>
+      <c r="N11" s="113"/>
+      <c r="O11" s="113"/>
+      <c r="P11" s="114"/>
     </row>
     <row r="12" spans="1:16" ht="30.75" thickBot="1">
       <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="152" t="s">
+      <c r="C12" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="152"/>
+      <c r="D12" s="115"/>
       <c r="E12" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="152" t="s">
+      <c r="G12" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="153"/>
+      <c r="H12" s="116"/>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="115" t="s">
+      <c r="C13" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="115"/>
+      <c r="D13" s="117"/>
       <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="2">
         <v>2.2046199999999998</v>
       </c>
-      <c r="G13" s="115" t="s">
+      <c r="G13" s="117" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="116"/>
-      <c r="J13" s="154" t="s">
+      <c r="H13" s="118"/>
+      <c r="J13" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="155"/>
-      <c r="L13" s="155"/>
-      <c r="M13" s="155"/>
-      <c r="N13" s="156"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="121"/>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="115" t="s">
+      <c r="C14" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="115"/>
+      <c r="D14" s="117"/>
       <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="2">
         <v>29.573499999999999</v>
       </c>
-      <c r="G14" s="115" t="s">
+      <c r="G14" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="116"/>
-      <c r="J14" s="135" t="s">
+      <c r="H14" s="118"/>
+      <c r="J14" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="136"/>
-      <c r="L14" s="135" t="s">
+      <c r="K14" s="123"/>
+      <c r="L14" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="115"/>
-      <c r="N14" s="116"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="118"/>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" s="115" t="s">
+      <c r="C15" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="115"/>
+      <c r="D15" s="117"/>
       <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="3">
         <v>28.349523125000001</v>
       </c>
-      <c r="G15" s="115" t="s">
+      <c r="G15" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="116"/>
-      <c r="J15" s="137" t="s">
+      <c r="H15" s="118"/>
+      <c r="J15" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="138"/>
-      <c r="L15" s="139" t="s">
+      <c r="K15" s="125"/>
+      <c r="L15" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="140"/>
-      <c r="N15" s="141"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="128"/>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" s="115" t="s">
+      <c r="C16" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="115"/>
+      <c r="D16" s="117"/>
       <c r="E16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="2">
         <v>1000</v>
       </c>
-      <c r="G16" s="115" t="s">
+      <c r="G16" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="116"/>
-      <c r="J16" s="144" t="s">
+      <c r="H16" s="118"/>
+      <c r="J16" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="145"/>
-      <c r="L16" s="139" t="s">
+      <c r="K16" s="132"/>
+      <c r="L16" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="140"/>
-      <c r="N16" s="141"/>
+      <c r="M16" s="127"/>
+      <c r="N16" s="128"/>
     </row>
     <row r="17" spans="1:20">
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="115" t="s">
+      <c r="C17" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="115"/>
+      <c r="D17" s="117"/>
       <c r="E17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="2">
         <v>1000</v>
       </c>
-      <c r="G17" s="115" t="s">
+      <c r="G17" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="116"/>
-      <c r="J17" s="146" t="s">
+      <c r="H17" s="118"/>
+      <c r="J17" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="147"/>
-      <c r="L17" s="139" t="s">
+      <c r="K17" s="134"/>
+      <c r="L17" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="M17" s="140"/>
-      <c r="N17" s="141"/>
+      <c r="M17" s="127"/>
+      <c r="N17" s="128"/>
     </row>
     <row r="18" spans="1:20" ht="15.75" thickBot="1">
       <c r="B18" s="1">
         <v>1</v>
       </c>
-      <c r="C18" s="115" t="s">
+      <c r="C18" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="115"/>
+      <c r="D18" s="117"/>
       <c r="E18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="2">
         <v>1000</v>
       </c>
-      <c r="G18" s="115" t="s">
+      <c r="G18" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="116"/>
-      <c r="J18" s="148" t="s">
+      <c r="H18" s="118"/>
+      <c r="J18" s="135" t="s">
         <v>30</v>
       </c>
-      <c r="K18" s="149"/>
-      <c r="L18" s="148" t="s">
+      <c r="K18" s="136"/>
+      <c r="L18" s="135" t="s">
         <v>31</v>
       </c>
-      <c r="M18" s="150"/>
-      <c r="N18" s="151"/>
+      <c r="M18" s="137"/>
+      <c r="N18" s="138"/>
     </row>
     <row r="19" spans="1:20">
       <c r="B19" s="1">
         <v>1</v>
       </c>
-      <c r="C19" s="115" t="s">
+      <c r="C19" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="115"/>
+      <c r="D19" s="117"/>
       <c r="E19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="3">
         <v>33.814022600000001</v>
       </c>
-      <c r="G19" s="115" t="s">
+      <c r="G19" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="116"/>
+      <c r="H19" s="118"/>
     </row>
     <row r="20" spans="1:20" ht="21.75" thickBot="1">
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="115" t="s">
+      <c r="C20" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="115"/>
+      <c r="D20" s="117"/>
       <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="3">
         <v>0.26417205235800001</v>
       </c>
-      <c r="G20" s="115" t="s">
+      <c r="G20" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="116"/>
-      <c r="J20" s="124" t="s">
+      <c r="H20" s="118"/>
+      <c r="J20" s="146" t="s">
         <v>35</v>
       </c>
-      <c r="K20" s="124"/>
-      <c r="L20" s="125" t="s">
+      <c r="K20" s="146"/>
+      <c r="L20" s="147" t="s">
         <v>130</v>
       </c>
-      <c r="M20" s="198"/>
-      <c r="N20" s="198"/>
+      <c r="M20" s="148"/>
+      <c r="N20" s="148"/>
     </row>
     <row r="21" spans="1:20">
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="115" t="s">
+      <c r="C21" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="115"/>
+      <c r="D21" s="117"/>
       <c r="E21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="3">
         <v>4.9289199999999997</v>
       </c>
-      <c r="G21" s="115" t="s">
+      <c r="G21" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="116"/>
-      <c r="M21" s="203">
+      <c r="H21" s="118"/>
+      <c r="M21" s="91">
         <v>15</v>
       </c>
-      <c r="N21" s="119" t="s">
+      <c r="N21" s="141" t="s">
         <v>39</v>
       </c>
-      <c r="O21" s="119"/>
-      <c r="P21" s="119"/>
-      <c r="Q21" s="119"/>
-      <c r="R21" s="120"/>
+      <c r="O21" s="141"/>
+      <c r="P21" s="141"/>
+      <c r="Q21" s="141"/>
+      <c r="R21" s="142"/>
     </row>
     <row r="22" spans="1:20" ht="15.6" customHeight="1">
       <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="115" t="s">
+      <c r="C22" s="117" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="115"/>
+      <c r="D22" s="117"/>
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="3">
         <v>3.28084</v>
       </c>
-      <c r="G22" s="115" t="s">
+      <c r="G22" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="116"/>
-      <c r="M22" s="205">
+      <c r="H22" s="118"/>
+      <c r="M22" s="93">
         <v>15</v>
       </c>
-      <c r="N22" s="117" t="s">
+      <c r="N22" s="163" t="s">
         <v>42</v>
       </c>
-      <c r="O22" s="117"/>
-      <c r="P22" s="117"/>
-      <c r="Q22" s="117"/>
-      <c r="R22" s="118"/>
+      <c r="O22" s="163"/>
+      <c r="P22" s="163"/>
+      <c r="Q22" s="163"/>
+      <c r="R22" s="164"/>
     </row>
     <row r="23" spans="1:20" ht="15.6" customHeight="1" thickBot="1">
       <c r="B23" s="4">
         <v>1</v>
       </c>
-      <c r="C23" s="142" t="s">
+      <c r="C23" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="142"/>
+      <c r="D23" s="129"/>
       <c r="E23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="5">
         <v>24</v>
       </c>
-      <c r="G23" s="142" t="s">
+      <c r="G23" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="H23" s="143"/>
-      <c r="M23" s="206">
+      <c r="H23" s="130"/>
+      <c r="M23" s="94">
         <v>16</v>
       </c>
-      <c r="N23" s="201" t="s">
+      <c r="N23" s="139" t="s">
         <v>44</v>
       </c>
-      <c r="O23" s="201"/>
-      <c r="P23" s="201"/>
-      <c r="Q23" s="201"/>
-      <c r="R23" s="202"/>
+      <c r="O23" s="139"/>
+      <c r="P23" s="139"/>
+      <c r="Q23" s="139"/>
+      <c r="R23" s="140"/>
     </row>
     <row r="24" spans="1:20" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A24" s="189" t="s">
+      <c r="A24" s="149" t="s">
         <v>131</v>
       </c>
-      <c r="B24" s="190"/>
-      <c r="C24" s="190"/>
-      <c r="D24" s="190"/>
-      <c r="E24" s="190"/>
-      <c r="F24" s="190"/>
-      <c r="G24" s="190"/>
-      <c r="H24" s="190"/>
-      <c r="I24" s="190"/>
-      <c r="J24" s="190"/>
-      <c r="K24" s="191"/>
-      <c r="M24" s="204">
+      <c r="B24" s="150"/>
+      <c r="C24" s="150"/>
+      <c r="D24" s="150"/>
+      <c r="E24" s="150"/>
+      <c r="F24" s="150"/>
+      <c r="G24" s="150"/>
+      <c r="H24" s="150"/>
+      <c r="I24" s="150"/>
+      <c r="J24" s="150"/>
+      <c r="K24" s="151"/>
+      <c r="M24" s="92">
         <v>16</v>
       </c>
-      <c r="N24" s="199" t="s">
+      <c r="N24" s="161" t="s">
         <v>132</v>
       </c>
-      <c r="O24" s="199"/>
-      <c r="P24" s="199"/>
-      <c r="Q24" s="199"/>
-      <c r="R24" s="200"/>
-      <c r="S24" s="207"/>
-      <c r="T24" s="208"/>
+      <c r="O24" s="161"/>
+      <c r="P24" s="161"/>
+      <c r="Q24" s="161"/>
+      <c r="R24" s="162"/>
+      <c r="S24" s="95"/>
+      <c r="T24" s="96"/>
     </row>
     <row r="25" spans="1:20" ht="15.75" hidden="1" thickBot="1">
-      <c r="A25" s="192"/>
-      <c r="B25" s="193"/>
-      <c r="C25" s="193"/>
-      <c r="D25" s="193"/>
-      <c r="E25" s="193"/>
-      <c r="F25" s="193"/>
-      <c r="G25" s="193"/>
-      <c r="H25" s="193"/>
-      <c r="I25" s="193"/>
-      <c r="J25" s="193"/>
-      <c r="K25" s="194"/>
+      <c r="A25" s="152"/>
+      <c r="B25" s="153"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="153"/>
+      <c r="J25" s="153"/>
+      <c r="K25" s="154"/>
       <c r="M25" s="83">
         <v>16</v>
       </c>
-      <c r="N25" s="121" t="s">
+      <c r="N25" s="143" t="s">
         <v>45</v>
       </c>
-      <c r="O25" s="122"/>
-      <c r="P25" s="122"/>
-      <c r="Q25" s="122"/>
-      <c r="R25" s="123"/>
+      <c r="O25" s="144"/>
+      <c r="P25" s="144"/>
+      <c r="Q25" s="144"/>
+      <c r="R25" s="145"/>
     </row>
     <row r="26" spans="1:20" hidden="1">
-      <c r="A26" s="192"/>
-      <c r="B26" s="193"/>
-      <c r="C26" s="193"/>
-      <c r="D26" s="193"/>
-      <c r="E26" s="193"/>
-      <c r="F26" s="193"/>
-      <c r="G26" s="193"/>
-      <c r="H26" s="193"/>
-      <c r="I26" s="193"/>
-      <c r="J26" s="193"/>
-      <c r="K26" s="194"/>
+      <c r="A26" s="152"/>
+      <c r="B26" s="153"/>
+      <c r="C26" s="153"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="153"/>
+      <c r="F26" s="153"/>
+      <c r="G26" s="153"/>
+      <c r="H26" s="153"/>
+      <c r="I26" s="153"/>
+      <c r="J26" s="153"/>
+      <c r="K26" s="154"/>
     </row>
     <row r="27" spans="1:20" hidden="1">
-      <c r="A27" s="192"/>
-      <c r="B27" s="193"/>
-      <c r="C27" s="193"/>
-      <c r="D27" s="193"/>
-      <c r="E27" s="193"/>
-      <c r="F27" s="193"/>
-      <c r="G27" s="193"/>
-      <c r="H27" s="193"/>
-      <c r="I27" s="193"/>
-      <c r="J27" s="193"/>
-      <c r="K27" s="194"/>
+      <c r="A27" s="152"/>
+      <c r="B27" s="153"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="153"/>
+      <c r="G27" s="153"/>
+      <c r="H27" s="153"/>
+      <c r="I27" s="153"/>
+      <c r="J27" s="153"/>
+      <c r="K27" s="154"/>
     </row>
     <row r="28" spans="1:20" hidden="1">
-      <c r="A28" s="192"/>
-      <c r="B28" s="193"/>
-      <c r="C28" s="193"/>
-      <c r="D28" s="193"/>
-      <c r="E28" s="193"/>
-      <c r="F28" s="193"/>
-      <c r="G28" s="193"/>
-      <c r="H28" s="193"/>
-      <c r="I28" s="193"/>
-      <c r="J28" s="193"/>
-      <c r="K28" s="194"/>
+      <c r="A28" s="152"/>
+      <c r="B28" s="153"/>
+      <c r="C28" s="153"/>
+      <c r="D28" s="153"/>
+      <c r="E28" s="153"/>
+      <c r="F28" s="153"/>
+      <c r="G28" s="153"/>
+      <c r="H28" s="153"/>
+      <c r="I28" s="153"/>
+      <c r="J28" s="153"/>
+      <c r="K28" s="154"/>
     </row>
     <row r="29" spans="1:20" hidden="1">
-      <c r="A29" s="192"/>
-      <c r="B29" s="193"/>
-      <c r="C29" s="193"/>
-      <c r="D29" s="193"/>
-      <c r="E29" s="193"/>
-      <c r="F29" s="193"/>
-      <c r="G29" s="193"/>
-      <c r="H29" s="193"/>
-      <c r="I29" s="193"/>
-      <c r="J29" s="193"/>
-      <c r="K29" s="194"/>
+      <c r="A29" s="152"/>
+      <c r="B29" s="153"/>
+      <c r="C29" s="153"/>
+      <c r="D29" s="153"/>
+      <c r="E29" s="153"/>
+      <c r="F29" s="153"/>
+      <c r="G29" s="153"/>
+      <c r="H29" s="153"/>
+      <c r="I29" s="153"/>
+      <c r="J29" s="153"/>
+      <c r="K29" s="154"/>
     </row>
     <row r="30" spans="1:20" hidden="1">
-      <c r="A30" s="192"/>
-      <c r="B30" s="193"/>
-      <c r="C30" s="193"/>
-      <c r="D30" s="193"/>
-      <c r="E30" s="193"/>
-      <c r="F30" s="193"/>
-      <c r="G30" s="193"/>
-      <c r="H30" s="193"/>
-      <c r="I30" s="193"/>
-      <c r="J30" s="193"/>
-      <c r="K30" s="194"/>
+      <c r="A30" s="152"/>
+      <c r="B30" s="153"/>
+      <c r="C30" s="153"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
+      <c r="F30" s="153"/>
+      <c r="G30" s="153"/>
+      <c r="H30" s="153"/>
+      <c r="I30" s="153"/>
+      <c r="J30" s="153"/>
+      <c r="K30" s="154"/>
     </row>
     <row r="31" spans="1:20" ht="116.25" customHeight="1" thickBot="1">
-      <c r="A31" s="195"/>
-      <c r="B31" s="196"/>
-      <c r="C31" s="196"/>
-      <c r="D31" s="196"/>
-      <c r="E31" s="196"/>
-      <c r="F31" s="196"/>
-      <c r="G31" s="196"/>
-      <c r="H31" s="196"/>
-      <c r="I31" s="196"/>
-      <c r="J31" s="196"/>
-      <c r="K31" s="197"/>
-      <c r="M31" s="209" t="s">
+      <c r="A31" s="155"/>
+      <c r="B31" s="156"/>
+      <c r="C31" s="156"/>
+      <c r="D31" s="156"/>
+      <c r="E31" s="156"/>
+      <c r="F31" s="156"/>
+      <c r="G31" s="156"/>
+      <c r="H31" s="156"/>
+      <c r="I31" s="156"/>
+      <c r="J31" s="156"/>
+      <c r="K31" s="157"/>
+      <c r="M31" s="158" t="s">
         <v>133</v>
       </c>
-      <c r="N31" s="210"/>
-      <c r="O31" s="210"/>
-      <c r="P31" s="210"/>
-      <c r="Q31" s="210"/>
-      <c r="R31" s="211"/>
+      <c r="N31" s="159"/>
+      <c r="O31" s="159"/>
+      <c r="P31" s="159"/>
+      <c r="Q31" s="159"/>
+      <c r="R31" s="160"/>
     </row>
     <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1">
       <c r="A32" s="11"/>
@@ -3432,24 +3487,24 @@
       <c r="C33" s="84"/>
       <c r="D33" s="84"/>
       <c r="E33" s="84"/>
-      <c r="F33" s="98" t="s">
-        <v>46</v>
-      </c>
-      <c r="G33" s="99"/>
-      <c r="H33" s="99"/>
-      <c r="I33" s="99"/>
-      <c r="J33" s="99"/>
-      <c r="K33" s="99"/>
-      <c r="L33" s="99"/>
-      <c r="M33" s="99"/>
-      <c r="N33" s="99"/>
-      <c r="O33" s="99"/>
-      <c r="P33" s="100"/>
+      <c r="F33" s="209" t="s">
+        <v>134</v>
+      </c>
+      <c r="G33" s="210"/>
+      <c r="H33" s="210"/>
+      <c r="I33" s="210"/>
+      <c r="J33" s="210"/>
+      <c r="K33" s="210"/>
+      <c r="L33" s="210"/>
+      <c r="M33" s="210"/>
+      <c r="N33" s="210"/>
+      <c r="O33" s="210"/>
+      <c r="P33" s="211"/>
       <c r="Q33" s="77"/>
     </row>
     <row r="34" spans="1:17" ht="30.75" thickBot="1">
-      <c r="A34" s="186"/>
-      <c r="B34" s="187"/>
+      <c r="A34" s="89"/>
+      <c r="B34" s="90"/>
       <c r="C34" s="47" t="s">
         <v>47</v>
       </c>
@@ -3495,10 +3550,10 @@
       <c r="Q34" s="78"/>
     </row>
     <row r="35" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="176" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="188"/>
+      <c r="B35" s="178"/>
       <c r="C35" s="62">
         <v>25</v>
       </c>
@@ -3525,9 +3580,9 @@
       <c r="J35" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="K35" s="112"/>
-      <c r="L35" s="112"/>
-      <c r="M35" s="112"/>
+      <c r="K35" s="175"/>
+      <c r="L35" s="175"/>
+      <c r="M35" s="175"/>
       <c r="N35" s="64" t="s">
         <v>10</v>
       </c>
@@ -3541,10 +3596,10 @@
       <c r="Q35" s="78"/>
     </row>
     <row r="36" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="176" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="177"/>
       <c r="C36" s="62">
         <v>2.5</v>
       </c>
@@ -3561,9 +3616,9 @@
       </c>
       <c r="I36" s="61"/>
       <c r="J36" s="65"/>
-      <c r="K36" s="112"/>
-      <c r="L36" s="112"/>
-      <c r="M36" s="112"/>
+      <c r="K36" s="175"/>
+      <c r="L36" s="175"/>
+      <c r="M36" s="175"/>
       <c r="N36" s="64" t="s">
         <v>10</v>
       </c>
@@ -3572,10 +3627,10 @@
       <c r="Q36" s="78"/>
     </row>
     <row r="37" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A37" s="110" t="s">
+      <c r="A37" s="173" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="111"/>
+      <c r="B37" s="174"/>
       <c r="C37" s="62">
         <v>5</v>
       </c>
@@ -3605,28 +3660,28 @@
       <c r="Q37" s="75"/>
     </row>
     <row r="38" spans="1:17" ht="19.5" thickBot="1">
-      <c r="A38" s="103" t="s">
+      <c r="A38" s="167" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="104"/>
-      <c r="C38" s="105"/>
-      <c r="D38" s="105"/>
-      <c r="E38" s="105"/>
-      <c r="F38" s="105"/>
-      <c r="G38" s="105"/>
-      <c r="H38" s="105"/>
-      <c r="I38" s="105"/>
-      <c r="J38" s="105"/>
-      <c r="K38" s="105"/>
-      <c r="L38" s="105"/>
-      <c r="M38" s="105"/>
-      <c r="N38" s="105"/>
-      <c r="O38" s="105"/>
-      <c r="P38" s="106"/>
+      <c r="B38" s="168"/>
+      <c r="C38" s="169"/>
+      <c r="D38" s="169"/>
+      <c r="E38" s="169"/>
+      <c r="F38" s="169"/>
+      <c r="G38" s="169"/>
+      <c r="H38" s="169"/>
+      <c r="I38" s="169"/>
+      <c r="J38" s="169"/>
+      <c r="K38" s="169"/>
+      <c r="L38" s="169"/>
+      <c r="M38" s="169"/>
+      <c r="N38" s="169"/>
+      <c r="O38" s="169"/>
+      <c r="P38" s="170"/>
     </row>
     <row r="39" spans="1:17" ht="30.75" thickBot="1">
-      <c r="A39" s="107"/>
-      <c r="B39" s="108"/>
+      <c r="A39" s="171"/>
+      <c r="B39" s="172"/>
       <c r="C39" s="18" t="s">
         <v>47</v>
       </c>
@@ -3671,10 +3726,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="176" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="177"/>
       <c r="C40" s="62" t="str">
         <f>IF(L$20="Your Name!", "Enter Name in L20",ROUND(50*Random!D21,1)+1)</f>
         <v>Enter Name in L20</v>
@@ -3692,9 +3747,9 @@
       </c>
       <c r="I40" s="61"/>
       <c r="J40" s="65"/>
-      <c r="K40" s="112"/>
-      <c r="L40" s="112"/>
-      <c r="M40" s="112"/>
+      <c r="K40" s="175"/>
+      <c r="L40" s="175"/>
+      <c r="M40" s="175"/>
       <c r="N40" s="64" t="s">
         <v>10</v>
       </c>
@@ -3702,10 +3757,10 @@
       <c r="P40" s="66"/>
     </row>
     <row r="41" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A41" s="101" t="s">
+      <c r="A41" s="165" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="102"/>
+      <c r="B41" s="166"/>
       <c r="C41" s="62" t="str">
         <f>IF(L$20="Your Name!", "Enter Name in L20",ROUND(50*Random!D22,1)+1)</f>
         <v>Enter Name in L20</v>
@@ -3735,20 +3790,36 @@
       <c r="P41" s="82"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="0cfGuQ1kMMCyKq8PbsihB5LIA8VirkeevZq0Ag9T/CwUBHeRtEDw/H0sy6usZwodltvfM6PvJXx8ariKtrVH4g==" saltValue="2ijSanNGCAUHhVXNfBCeQA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="dB23+XZH+Oa0Huu6tUAJA79GWafRoG1zQyItfVAWpUgqFL4v2gk8yvHQ7YMxAU8GJxGPHpCzDU7yRz0ujc0p5g==" saltValue="7CvP4XnLWnuOI8Pc8+HWBw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="56">
-    <mergeCell ref="A1:P11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F33:P33"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="N22:R22"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="N23:R23"/>
+    <mergeCell ref="N21:R21"/>
+    <mergeCell ref="N25:R25"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="A24:K31"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="M31:R31"/>
+    <mergeCell ref="N24:R24"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="L14:N14"/>
     <mergeCell ref="J15:K15"/>
@@ -3765,34 +3836,18 @@
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="N23:R23"/>
-    <mergeCell ref="N21:R21"/>
-    <mergeCell ref="N25:R25"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="A24:K31"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="M31:R31"/>
-    <mergeCell ref="N24:R24"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="N22:R22"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="F33:P33"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A38:P38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A1:P11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:N13"/>
   </mergeCells>
   <conditionalFormatting sqref="F36:F37 I36:I37 O36:O37 L37 F40:F41 I40:I41 O40:O41 L41">
     <cfRule type="expression" dxfId="2" priority="2">
@@ -3804,6 +3859,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -5874,590 +5930,590 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="106" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="127"/>
-      <c r="P1" s="128"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="108"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="129"/>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="130"/>
-      <c r="P2" s="131"/>
+      <c r="A2" s="109"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="111"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="129"/>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="131"/>
+      <c r="A3" s="109"/>
+      <c r="B3" s="110"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="110"/>
+      <c r="E3" s="110"/>
+      <c r="F3" s="110"/>
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="110"/>
+      <c r="L3" s="110"/>
+      <c r="M3" s="110"/>
+      <c r="N3" s="110"/>
+      <c r="O3" s="110"/>
+      <c r="P3" s="111"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="129"/>
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
-      <c r="D4" s="130"/>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
-      <c r="O4" s="130"/>
-      <c r="P4" s="131"/>
+      <c r="A4" s="109"/>
+      <c r="B4" s="110"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="110"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110"/>
+      <c r="L4" s="110"/>
+      <c r="M4" s="110"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="110"/>
+      <c r="P4" s="111"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="129"/>
-      <c r="B5" s="130"/>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
-      <c r="I5" s="130"/>
-      <c r="J5" s="130"/>
-      <c r="K5" s="130"/>
-      <c r="L5" s="130"/>
-      <c r="M5" s="130"/>
-      <c r="N5" s="130"/>
-      <c r="O5" s="130"/>
-      <c r="P5" s="131"/>
+      <c r="A5" s="109"/>
+      <c r="B5" s="110"/>
+      <c r="C5" s="110"/>
+      <c r="D5" s="110"/>
+      <c r="E5" s="110"/>
+      <c r="F5" s="110"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="110"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="110"/>
+      <c r="L5" s="110"/>
+      <c r="M5" s="110"/>
+      <c r="N5" s="110"/>
+      <c r="O5" s="110"/>
+      <c r="P5" s="111"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="129"/>
-      <c r="B6" s="130"/>
-      <c r="C6" s="130"/>
-      <c r="D6" s="130"/>
-      <c r="E6" s="130"/>
-      <c r="F6" s="130"/>
-      <c r="G6" s="130"/>
-      <c r="H6" s="130"/>
-      <c r="I6" s="130"/>
-      <c r="J6" s="130"/>
-      <c r="K6" s="130"/>
-      <c r="L6" s="130"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="130"/>
-      <c r="O6" s="130"/>
-      <c r="P6" s="131"/>
+      <c r="A6" s="109"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="110"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="110"/>
+      <c r="M6" s="110"/>
+      <c r="N6" s="110"/>
+      <c r="O6" s="110"/>
+      <c r="P6" s="111"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="129"/>
-      <c r="B7" s="130"/>
-      <c r="C7" s="130"/>
-      <c r="D7" s="130"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="130"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="130"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="130"/>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="130"/>
-      <c r="O7" s="130"/>
-      <c r="P7" s="131"/>
+      <c r="A7" s="109"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="110"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="110"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="111"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="129"/>
-      <c r="B8" s="130"/>
-      <c r="C8" s="130"/>
-      <c r="D8" s="130"/>
-      <c r="E8" s="130"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="130"/>
-      <c r="H8" s="130"/>
-      <c r="I8" s="130"/>
-      <c r="J8" s="130"/>
-      <c r="K8" s="130"/>
-      <c r="L8" s="130"/>
-      <c r="M8" s="130"/>
-      <c r="N8" s="130"/>
-      <c r="O8" s="130"/>
-      <c r="P8" s="131"/>
+      <c r="A8" s="109"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="110"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="110"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="110"/>
+      <c r="H8" s="110"/>
+      <c r="I8" s="110"/>
+      <c r="J8" s="110"/>
+      <c r="K8" s="110"/>
+      <c r="L8" s="110"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="110"/>
+      <c r="O8" s="110"/>
+      <c r="P8" s="111"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="129"/>
-      <c r="B9" s="130"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="130"/>
-      <c r="G9" s="130"/>
-      <c r="H9" s="130"/>
-      <c r="I9" s="130"/>
-      <c r="J9" s="130"/>
-      <c r="K9" s="130"/>
-      <c r="L9" s="130"/>
-      <c r="M9" s="130"/>
-      <c r="N9" s="130"/>
-      <c r="O9" s="130"/>
-      <c r="P9" s="131"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="110"/>
+      <c r="C9" s="110"/>
+      <c r="D9" s="110"/>
+      <c r="E9" s="110"/>
+      <c r="F9" s="110"/>
+      <c r="G9" s="110"/>
+      <c r="H9" s="110"/>
+      <c r="I9" s="110"/>
+      <c r="J9" s="110"/>
+      <c r="K9" s="110"/>
+      <c r="L9" s="110"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="110"/>
+      <c r="O9" s="110"/>
+      <c r="P9" s="111"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="129"/>
-      <c r="B10" s="130"/>
-      <c r="C10" s="130"/>
-      <c r="D10" s="130"/>
-      <c r="E10" s="130"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="130"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="130"/>
-      <c r="K10" s="130"/>
-      <c r="L10" s="130"/>
-      <c r="M10" s="130"/>
-      <c r="N10" s="130"/>
-      <c r="O10" s="130"/>
-      <c r="P10" s="131"/>
+      <c r="A10" s="109"/>
+      <c r="B10" s="110"/>
+      <c r="C10" s="110"/>
+      <c r="D10" s="110"/>
+      <c r="E10" s="110"/>
+      <c r="F10" s="110"/>
+      <c r="G10" s="110"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="110"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="110"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="111"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A11" s="132"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="133"/>
-      <c r="K11" s="133"/>
-      <c r="L11" s="133"/>
-      <c r="M11" s="133"/>
-      <c r="N11" s="133"/>
-      <c r="O11" s="133"/>
-      <c r="P11" s="134"/>
+      <c r="A11" s="112"/>
+      <c r="B11" s="113"/>
+      <c r="C11" s="113"/>
+      <c r="D11" s="113"/>
+      <c r="E11" s="113"/>
+      <c r="F11" s="113"/>
+      <c r="G11" s="113"/>
+      <c r="H11" s="113"/>
+      <c r="I11" s="113"/>
+      <c r="J11" s="113"/>
+      <c r="K11" s="113"/>
+      <c r="L11" s="113"/>
+      <c r="M11" s="113"/>
+      <c r="N11" s="113"/>
+      <c r="O11" s="113"/>
+      <c r="P11" s="114"/>
     </row>
     <row r="12" spans="1:16" ht="30.75" thickBot="1">
       <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="152" t="s">
+      <c r="C12" s="115" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="152"/>
+      <c r="D12" s="115"/>
       <c r="E12" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="152" t="s">
+      <c r="G12" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="153"/>
+      <c r="H12" s="116"/>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="115" t="s">
+      <c r="C13" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="115"/>
+      <c r="D13" s="117"/>
       <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="2">
         <v>2.2046199999999998</v>
       </c>
-      <c r="G13" s="115" t="s">
+      <c r="G13" s="117" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="116"/>
-      <c r="J13" s="154" t="s">
+      <c r="H13" s="118"/>
+      <c r="J13" s="119" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="155"/>
-      <c r="L13" s="155"/>
-      <c r="M13" s="155"/>
-      <c r="N13" s="156"/>
+      <c r="K13" s="120"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="121"/>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="115" t="s">
+      <c r="C14" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="115"/>
+      <c r="D14" s="117"/>
       <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="2">
         <v>29.573499999999999</v>
       </c>
-      <c r="G14" s="115" t="s">
+      <c r="G14" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="116"/>
-      <c r="J14" s="135" t="s">
+      <c r="H14" s="118"/>
+      <c r="J14" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="136"/>
-      <c r="L14" s="135" t="s">
+      <c r="K14" s="123"/>
+      <c r="L14" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="115"/>
-      <c r="N14" s="116"/>
+      <c r="M14" s="117"/>
+      <c r="N14" s="118"/>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" s="115" t="s">
+      <c r="C15" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="115"/>
+      <c r="D15" s="117"/>
       <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="3">
         <v>28.349523125000001</v>
       </c>
-      <c r="G15" s="115" t="s">
+      <c r="G15" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="116"/>
-      <c r="J15" s="137" t="s">
+      <c r="H15" s="118"/>
+      <c r="J15" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="138"/>
-      <c r="L15" s="139" t="s">
+      <c r="K15" s="125"/>
+      <c r="L15" s="126" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="140"/>
-      <c r="N15" s="141"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="128"/>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" s="115" t="s">
+      <c r="C16" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="115"/>
+      <c r="D16" s="117"/>
       <c r="E16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="2">
         <v>1000</v>
       </c>
-      <c r="G16" s="115" t="s">
+      <c r="G16" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="116"/>
-      <c r="J16" s="144" t="s">
+      <c r="H16" s="118"/>
+      <c r="J16" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="145"/>
-      <c r="L16" s="139" t="s">
+      <c r="K16" s="132"/>
+      <c r="L16" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="140"/>
-      <c r="N16" s="141"/>
+      <c r="M16" s="127"/>
+      <c r="N16" s="128"/>
     </row>
     <row r="17" spans="1:14">
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="115" t="s">
+      <c r="C17" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="115"/>
+      <c r="D17" s="117"/>
       <c r="E17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="2">
         <v>1000</v>
       </c>
-      <c r="G17" s="115" t="s">
+      <c r="G17" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="116"/>
-      <c r="J17" s="146" t="s">
+      <c r="H17" s="118"/>
+      <c r="J17" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="147"/>
-      <c r="L17" s="139" t="s">
+      <c r="K17" s="134"/>
+      <c r="L17" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="M17" s="140"/>
-      <c r="N17" s="141"/>
+      <c r="M17" s="127"/>
+      <c r="N17" s="128"/>
     </row>
     <row r="18" spans="1:14" ht="15.75" thickBot="1">
       <c r="B18" s="1">
         <v>1</v>
       </c>
-      <c r="C18" s="115" t="s">
+      <c r="C18" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="115"/>
+      <c r="D18" s="117"/>
       <c r="E18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="2">
         <v>1000</v>
       </c>
-      <c r="G18" s="115" t="s">
+      <c r="G18" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="116"/>
-      <c r="J18" s="148" t="s">
+      <c r="H18" s="118"/>
+      <c r="J18" s="135" t="s">
         <v>30</v>
       </c>
-      <c r="K18" s="149"/>
-      <c r="L18" s="148" t="s">
+      <c r="K18" s="136"/>
+      <c r="L18" s="135" t="s">
         <v>31</v>
       </c>
-      <c r="M18" s="150"/>
-      <c r="N18" s="151"/>
+      <c r="M18" s="137"/>
+      <c r="N18" s="138"/>
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="1">
         <v>1</v>
       </c>
-      <c r="C19" s="115" t="s">
+      <c r="C19" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="115"/>
+      <c r="D19" s="117"/>
       <c r="E19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="3">
         <v>33.814022600000001</v>
       </c>
-      <c r="G19" s="115" t="s">
+      <c r="G19" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="116"/>
+      <c r="H19" s="118"/>
     </row>
     <row r="20" spans="1:14">
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="115" t="s">
+      <c r="C20" s="117" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="115"/>
+      <c r="D20" s="117"/>
       <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="3">
         <v>0.26417205235800001</v>
       </c>
-      <c r="G20" s="115" t="s">
+      <c r="G20" s="117" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="116"/>
+      <c r="H20" s="118"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="115" t="s">
+      <c r="C21" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="115"/>
+      <c r="D21" s="117"/>
       <c r="E21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="3">
         <v>4.9289199999999997</v>
       </c>
-      <c r="G21" s="115" t="s">
+      <c r="G21" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="116"/>
+      <c r="H21" s="118"/>
     </row>
     <row r="22" spans="1:14">
       <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="115" t="s">
+      <c r="C22" s="117" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="115"/>
+      <c r="D22" s="117"/>
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="3">
         <v>3.28084</v>
       </c>
-      <c r="G22" s="115" t="s">
+      <c r="G22" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="116"/>
+      <c r="H22" s="118"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" thickBot="1">
       <c r="B23" s="4">
         <v>1</v>
       </c>
-      <c r="C23" s="142" t="s">
+      <c r="C23" s="129" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="142"/>
+      <c r="D23" s="129"/>
       <c r="E23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="5">
         <v>24</v>
       </c>
-      <c r="G23" s="142" t="s">
+      <c r="G23" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="H23" s="143"/>
+      <c r="H23" s="130"/>
     </row>
     <row r="24" spans="1:14" ht="15" customHeight="1">
-      <c r="A24" s="126" t="s">
+      <c r="A24" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="127"/>
-      <c r="C24" s="127"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="127"/>
-      <c r="H24" s="127"/>
-      <c r="I24" s="127"/>
-      <c r="J24" s="127"/>
-      <c r="K24" s="128"/>
+      <c r="B24" s="107"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="107"/>
+      <c r="E24" s="107"/>
+      <c r="F24" s="107"/>
+      <c r="G24" s="107"/>
+      <c r="H24" s="107"/>
+      <c r="I24" s="107"/>
+      <c r="J24" s="107"/>
+      <c r="K24" s="108"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="129"/>
-      <c r="B25" s="130"/>
-      <c r="C25" s="130"/>
-      <c r="D25" s="130"/>
-      <c r="E25" s="130"/>
-      <c r="F25" s="130"/>
-      <c r="G25" s="130"/>
-      <c r="H25" s="130"/>
-      <c r="I25" s="130"/>
-      <c r="J25" s="130"/>
-      <c r="K25" s="131"/>
+      <c r="A25" s="109"/>
+      <c r="B25" s="110"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="111"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="129"/>
-      <c r="B26" s="130"/>
-      <c r="C26" s="130"/>
-      <c r="D26" s="130"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="130"/>
-      <c r="G26" s="130"/>
-      <c r="H26" s="130"/>
-      <c r="I26" s="130"/>
-      <c r="J26" s="130"/>
-      <c r="K26" s="131"/>
+      <c r="A26" s="109"/>
+      <c r="B26" s="110"/>
+      <c r="C26" s="110"/>
+      <c r="D26" s="110"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
+      <c r="G26" s="110"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="110"/>
+      <c r="K26" s="111"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="129"/>
-      <c r="B27" s="130"/>
-      <c r="C27" s="130"/>
-      <c r="D27" s="130"/>
-      <c r="E27" s="130"/>
-      <c r="F27" s="130"/>
-      <c r="G27" s="130"/>
-      <c r="H27" s="130"/>
-      <c r="I27" s="130"/>
-      <c r="J27" s="130"/>
-      <c r="K27" s="131"/>
+      <c r="A27" s="109"/>
+      <c r="B27" s="110"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="110"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
+      <c r="G27" s="110"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="111"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="129"/>
-      <c r="B28" s="130"/>
-      <c r="C28" s="130"/>
-      <c r="D28" s="130"/>
-      <c r="E28" s="130"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="130"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="130"/>
-      <c r="J28" s="130"/>
-      <c r="K28" s="131"/>
+      <c r="A28" s="109"/>
+      <c r="B28" s="110"/>
+      <c r="C28" s="110"/>
+      <c r="D28" s="110"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
+      <c r="G28" s="110"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="111"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="129"/>
-      <c r="B29" s="130"/>
-      <c r="C29" s="130"/>
-      <c r="D29" s="130"/>
-      <c r="E29" s="130"/>
-      <c r="F29" s="130"/>
-      <c r="G29" s="130"/>
-      <c r="H29" s="130"/>
-      <c r="I29" s="130"/>
-      <c r="J29" s="130"/>
-      <c r="K29" s="131"/>
+      <c r="A29" s="109"/>
+      <c r="B29" s="110"/>
+      <c r="C29" s="110"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
+      <c r="G29" s="110"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="110"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="111"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="129"/>
-      <c r="B30" s="130"/>
-      <c r="C30" s="130"/>
-      <c r="D30" s="130"/>
-      <c r="E30" s="130"/>
-      <c r="F30" s="130"/>
-      <c r="G30" s="130"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="130"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="131"/>
+      <c r="A30" s="109"/>
+      <c r="B30" s="110"/>
+      <c r="C30" s="110"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="110"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="110"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="111"/>
     </row>
     <row r="31" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A31" s="132"/>
-      <c r="B31" s="133"/>
-      <c r="C31" s="133"/>
-      <c r="D31" s="133"/>
-      <c r="E31" s="133"/>
-      <c r="F31" s="133"/>
-      <c r="G31" s="133"/>
-      <c r="H31" s="133"/>
-      <c r="I31" s="133"/>
-      <c r="J31" s="133"/>
-      <c r="K31" s="134"/>
+      <c r="A31" s="112"/>
+      <c r="B31" s="113"/>
+      <c r="C31" s="113"/>
+      <c r="D31" s="113"/>
+      <c r="E31" s="113"/>
+      <c r="F31" s="113"/>
+      <c r="G31" s="113"/>
+      <c r="H31" s="113"/>
+      <c r="I31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="114"/>
     </row>
     <row r="32" spans="1:14" ht="15.75" thickBot="1">
       <c r="A32" s="11"/>
@@ -6473,28 +6529,28 @@
       <c r="K32" s="10"/>
     </row>
     <row r="33" spans="1:17" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A33" s="174" t="s">
+      <c r="A33" s="182" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="175"/>
-      <c r="C33" s="175"/>
-      <c r="D33" s="175"/>
-      <c r="E33" s="175"/>
-      <c r="F33" s="175"/>
-      <c r="G33" s="175"/>
-      <c r="H33" s="175"/>
-      <c r="I33" s="175"/>
-      <c r="J33" s="175"/>
-      <c r="K33" s="175"/>
-      <c r="L33" s="175"/>
-      <c r="M33" s="175"/>
-      <c r="N33" s="175"/>
-      <c r="O33" s="175"/>
-      <c r="P33" s="176"/>
+      <c r="B33" s="183"/>
+      <c r="C33" s="183"/>
+      <c r="D33" s="183"/>
+      <c r="E33" s="183"/>
+      <c r="F33" s="183"/>
+      <c r="G33" s="183"/>
+      <c r="H33" s="183"/>
+      <c r="I33" s="183"/>
+      <c r="J33" s="183"/>
+      <c r="K33" s="183"/>
+      <c r="L33" s="183"/>
+      <c r="M33" s="183"/>
+      <c r="N33" s="183"/>
+      <c r="O33" s="183"/>
+      <c r="P33" s="184"/>
     </row>
     <row r="34" spans="1:17" ht="30.75" thickBot="1">
-      <c r="A34" s="109"/>
-      <c r="B34" s="168"/>
+      <c r="A34" s="185"/>
+      <c r="B34" s="186"/>
       <c r="C34" s="9" t="s">
         <v>47</v>
       </c>
@@ -6542,10 +6598,10 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="45.75" customHeight="1" thickBot="1">
-      <c r="A35" s="171" t="s">
+      <c r="A35" s="179" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="172"/>
+      <c r="B35" s="180"/>
       <c r="C35" s="14">
         <v>25</v>
       </c>
@@ -6572,9 +6628,9 @@
       <c r="J35" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="K35" s="173"/>
-      <c r="L35" s="173"/>
-      <c r="M35" s="173"/>
+      <c r="K35" s="181"/>
+      <c r="L35" s="181"/>
+      <c r="M35" s="181"/>
       <c r="N35" s="35" t="s">
         <v>10</v>
       </c>
@@ -6590,10 +6646,10 @@
       </c>
     </row>
     <row r="36" spans="1:17" ht="33.950000000000003" customHeight="1" thickBot="1">
-      <c r="A36" s="159" t="s">
+      <c r="A36" s="189" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="160"/>
+      <c r="B36" s="190"/>
       <c r="C36" s="14">
         <v>2.5</v>
       </c>
@@ -6620,9 +6676,9 @@
       <c r="J36" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="K36" s="161"/>
-      <c r="L36" s="112"/>
-      <c r="M36" s="162"/>
+      <c r="K36" s="191"/>
+      <c r="L36" s="175"/>
+      <c r="M36" s="192"/>
       <c r="N36" s="35" t="s">
         <v>10</v>
       </c>
@@ -6636,10 +6692,10 @@
       <c r="Q36" s="12"/>
     </row>
     <row r="37" spans="1:17" ht="48.6" customHeight="1" thickBot="1">
-      <c r="A37" s="163" t="s">
+      <c r="A37" s="193" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="164"/>
+      <c r="B37" s="194"/>
       <c r="C37" s="14">
         <v>5</v>
       </c>
@@ -6689,28 +6745,28 @@
       <c r="Q37" s="13"/>
     </row>
     <row r="38" spans="1:17" ht="19.5" thickBot="1">
-      <c r="A38" s="165" t="s">
+      <c r="A38" s="195" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="166"/>
-      <c r="C38" s="166"/>
-      <c r="D38" s="166"/>
-      <c r="E38" s="166"/>
-      <c r="F38" s="166"/>
-      <c r="G38" s="166"/>
-      <c r="H38" s="166"/>
-      <c r="I38" s="166"/>
-      <c r="J38" s="166"/>
-      <c r="K38" s="166"/>
-      <c r="L38" s="166"/>
-      <c r="M38" s="166"/>
-      <c r="N38" s="166"/>
-      <c r="O38" s="166"/>
-      <c r="P38" s="167"/>
+      <c r="B38" s="196"/>
+      <c r="C38" s="196"/>
+      <c r="D38" s="196"/>
+      <c r="E38" s="196"/>
+      <c r="F38" s="196"/>
+      <c r="G38" s="196"/>
+      <c r="H38" s="196"/>
+      <c r="I38" s="196"/>
+      <c r="J38" s="196"/>
+      <c r="K38" s="196"/>
+      <c r="L38" s="196"/>
+      <c r="M38" s="196"/>
+      <c r="N38" s="196"/>
+      <c r="O38" s="196"/>
+      <c r="P38" s="197"/>
     </row>
     <row r="39" spans="1:17" ht="30.75" thickBot="1">
-      <c r="A39" s="109"/>
-      <c r="B39" s="168"/>
+      <c r="A39" s="185"/>
+      <c r="B39" s="186"/>
       <c r="C39" s="18" t="s">
         <v>47</v>
       </c>
@@ -6755,10 +6811,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" ht="48.95" customHeight="1" thickBot="1">
-      <c r="A40" s="159" t="s">
+      <c r="A40" s="189" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="160"/>
+      <c r="B40" s="190"/>
       <c r="C40" s="19" t="str">
         <f>Conversions!C40</f>
         <v>Enter Name in L20</v>
@@ -6786,9 +6842,9 @@
       <c r="J40" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="K40" s="169"/>
-      <c r="L40" s="169"/>
-      <c r="M40" s="170"/>
+      <c r="K40" s="198"/>
+      <c r="L40" s="198"/>
+      <c r="M40" s="199"/>
       <c r="N40" s="26" t="s">
         <v>10</v>
       </c>
@@ -6801,10 +6857,10 @@
       </c>
     </row>
     <row r="41" spans="1:17" ht="48.95" customHeight="1" thickBot="1">
-      <c r="A41" s="157" t="s">
+      <c r="A41" s="187" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="158"/>
+      <c r="B41" s="188"/>
       <c r="C41" s="20" t="str">
         <f>Conversions!C41</f>
         <v>Enter Name in L20</v>
@@ -6855,34 +6911,14 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A1:P11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="K40:M40"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="C20:D20"/>
@@ -6896,14 +6932,34 @@
     <mergeCell ref="A24:K31"/>
     <mergeCell ref="A33:P33"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:P38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="A1:P11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:N13"/>
   </mergeCells>
   <conditionalFormatting sqref="F40 I40">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -6926,34 +6982,34 @@
   <sheetData>
     <row r="1" spans="2:6" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:6" ht="26.1" customHeight="1">
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="200" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="179"/>
+      <c r="C2" s="201"/>
+      <c r="D2" s="201"/>
+      <c r="E2" s="201"/>
+      <c r="F2" s="202"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="180"/>
-      <c r="C3" s="181"/>
-      <c r="D3" s="181"/>
-      <c r="E3" s="181"/>
-      <c r="F3" s="182"/>
+      <c r="B3" s="203"/>
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="204"/>
+      <c r="F3" s="205"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="180"/>
-      <c r="C4" s="181"/>
-      <c r="D4" s="181"/>
-      <c r="E4" s="181"/>
-      <c r="F4" s="182"/>
+      <c r="B4" s="203"/>
+      <c r="C4" s="204"/>
+      <c r="D4" s="204"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="205"/>
     </row>
     <row r="5" spans="2:6" ht="15.75" thickBot="1">
-      <c r="B5" s="183"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
-      <c r="F5" s="185"/>
+      <c r="B5" s="206"/>
+      <c r="C5" s="207"/>
+      <c r="D5" s="207"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6964,15 +7020,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -7189,6 +7236,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7200,14 +7256,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF3B6B4C-EC0E-4746-BC50-2C3213BAC25B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75299CF-40C1-4653-959B-0AE66E133E77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7226,6 +7274,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF3B6B4C-EC0E-4746-BC50-2C3213BAC25B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D29BAF0-14B6-4E1B-BA72-51F7164DDA8E}">
   <ds:schemaRefs>
